--- a/LoanOfficer-A/2023/74 sanatombi.xlsx
+++ b/LoanOfficer-A/2023/74 sanatombi.xlsx
@@ -602,7 +602,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -804,7 +804,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -856,9 +856,15 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="1"/>
+      <c r="B3" s="3">
+        <v>45584</v>
+      </c>
+      <c r="C3" s="4">
+        <v>100</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
       <c r="E3" s="1">
         <v>31</v>
       </c>
@@ -882,9 +888,15 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="3">
+        <v>45585</v>
+      </c>
+      <c r="C4" s="4">
+        <v>100</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
       <c r="E4" s="1">
         <v>32</v>
       </c>
@@ -908,9 +920,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>45586</v>
+      </c>
+      <c r="C5" s="4">
+        <v>100</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -934,9 +952,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45587</v>
+      </c>
+      <c r="C6" s="4">
+        <v>100</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -960,9 +984,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45588</v>
+      </c>
+      <c r="C7" s="4">
+        <v>100</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -986,9 +1016,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45591</v>
+      </c>
+      <c r="C8" s="4">
+        <v>100</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1012,9 +1048,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45591</v>
+      </c>
+      <c r="C9" s="4">
+        <v>100</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1038,9 +1080,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45592</v>
+      </c>
+      <c r="C10" s="4">
+        <v>100</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1064,9 +1112,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45593</v>
+      </c>
+      <c r="C11" s="4">
+        <v>100</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1090,9 +1144,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45594</v>
+      </c>
+      <c r="C12" s="4">
+        <v>100</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>

--- a/LoanOfficer-A/2023/74 sanatombi.xlsx
+++ b/LoanOfficer-A/2023/74 sanatombi.xlsx
@@ -602,7 +602,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -804,7 +804,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>11000</v>
+        <v>10900</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1176,9 +1176,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45616</v>
+      </c>
+      <c r="C13" s="4">
+        <v>100</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>

--- a/LoanOfficer-A/2023/74 sanatombi.xlsx
+++ b/LoanOfficer-A/2023/74 sanatombi.xlsx
@@ -602,7 +602,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -804,7 +804,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>10900</v>
+        <v>10400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1208,9 +1208,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45623</v>
+      </c>
+      <c r="C14" s="4">
+        <v>100</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1234,9 +1240,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45623</v>
+      </c>
+      <c r="C15" s="4">
+        <v>100</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1260,9 +1272,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45623</v>
+      </c>
+      <c r="C16" s="4">
+        <v>100</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1286,9 +1304,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45623</v>
+      </c>
+      <c r="C17" s="4">
+        <v>100</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1312,9 +1336,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45623</v>
+      </c>
+      <c r="C18" s="4">
+        <v>100</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>

--- a/LoanOfficer-A/2023/74 sanatombi.xlsx
+++ b/LoanOfficer-A/2023/74 sanatombi.xlsx
@@ -97,7 +97,7 @@
     <t>TEACHER</t>
   </si>
   <si>
-    <t>sanatombi</t>
+    <t>Date of completion</t>
   </si>
 </sst>
 </file>
@@ -213,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -280,6 +280,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -602,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -804,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -813,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -828,9 +831,12 @@
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>24</v>
+      </c>
+      <c r="G2" s="23">
+        <f>B3+G1-1</f>
+        <v>45703</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -839,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -848,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>10400</v>
+        <v>9400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1368,9 +1374,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45669</v>
+      </c>
+      <c r="C19" s="4">
+        <v>100</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1394,9 +1406,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45669</v>
+      </c>
+      <c r="C20" s="4">
+        <v>100</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1420,9 +1438,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45669</v>
+      </c>
+      <c r="C21" s="4">
+        <v>100</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1446,9 +1470,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45669</v>
+      </c>
+      <c r="C22" s="4">
+        <v>100</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1472,9 +1502,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45669</v>
+      </c>
+      <c r="C23" s="4">
+        <v>100</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1498,9 +1534,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45669</v>
+      </c>
+      <c r="C24" s="4">
+        <v>100</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1524,9 +1566,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45669</v>
+      </c>
+      <c r="C25" s="4">
+        <v>100</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1550,9 +1598,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45669</v>
+      </c>
+      <c r="C26" s="4">
+        <v>100</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1576,9 +1630,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45669</v>
+      </c>
+      <c r="C27" s="4">
+        <v>100</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1602,9 +1662,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45669</v>
+      </c>
+      <c r="C28" s="4">
+        <v>100</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>

--- a/LoanOfficer-A/2023/74 sanatombi.xlsx
+++ b/LoanOfficer-A/2023/74 sanatombi.xlsx
@@ -275,14 +275,14 @@
     <xf numFmtId="15" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -623,8 +623,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
@@ -699,20 +699,20 @@
       <c r="C16" s="14"/>
     </row>
     <row r="17" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="22"/>
+      <c r="C17" s="23"/>
     </row>
     <row r="19" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
     </row>
     <row r="21" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="22"/>
+      <c r="C21" s="23"/>
     </row>
     <row r="22" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B22" s="14"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>2600</v>
+        <v>5100</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       <c r="F2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="23">
+      <c r="G2" s="21">
         <f>B3+G1-1</f>
         <v>45703</v>
       </c>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>9400</v>
+        <v>6900</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -874,9 +874,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45678</v>
+      </c>
+      <c r="G3" s="4">
+        <v>100</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -906,9 +912,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45678</v>
+      </c>
+      <c r="G4" s="4">
+        <v>100</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -938,9 +950,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45678</v>
+      </c>
+      <c r="G5" s="4">
+        <v>100</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -970,9 +988,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45678</v>
+      </c>
+      <c r="G6" s="4">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -1002,9 +1026,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45678</v>
+      </c>
+      <c r="G7" s="4">
+        <v>100</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1034,9 +1064,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45678</v>
+      </c>
+      <c r="G8" s="4">
+        <v>100</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1066,9 +1102,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45684</v>
+      </c>
+      <c r="G9" s="4">
+        <v>100</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1098,9 +1140,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45684</v>
+      </c>
+      <c r="G10" s="4">
+        <v>100</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1130,9 +1178,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45684</v>
+      </c>
+      <c r="G11" s="4">
+        <v>100</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1162,9 +1216,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45684</v>
+      </c>
+      <c r="G12" s="4">
+        <v>100</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1194,9 +1254,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45684</v>
+      </c>
+      <c r="G13" s="4">
+        <v>100</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1226,9 +1292,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45684</v>
+      </c>
+      <c r="G14" s="4">
+        <v>100</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1258,9 +1330,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45684</v>
+      </c>
+      <c r="G15" s="4">
+        <v>100</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1290,9 +1368,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45684</v>
+      </c>
+      <c r="G16" s="4">
+        <v>100</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>
@@ -1322,9 +1406,15 @@
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>45684</v>
+      </c>
+      <c r="G17" s="4">
+        <v>100</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>
@@ -1354,9 +1444,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45684</v>
+      </c>
+      <c r="G18" s="4">
+        <v>100</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
@@ -1386,9 +1482,15 @@
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>45691</v>
+      </c>
+      <c r="G19" s="4">
+        <v>100</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>
@@ -1418,9 +1520,15 @@
       <c r="E20" s="1">
         <v>48</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
+      <c r="F20" s="3">
+        <v>45691</v>
+      </c>
+      <c r="G20" s="4">
+        <v>100</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
       <c r="I20" s="1">
         <v>78</v>
       </c>
@@ -1450,9 +1558,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>45691</v>
+      </c>
+      <c r="G21" s="4">
+        <v>100</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>
@@ -1482,9 +1596,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>45691</v>
+      </c>
+      <c r="G22" s="4">
+        <v>100</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>
@@ -1514,9 +1634,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>45691</v>
+      </c>
+      <c r="G23" s="4">
+        <v>100</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>
@@ -1694,9 +1820,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45678</v>
+      </c>
+      <c r="C29" s="4">
+        <v>100</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1720,9 +1852,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45678</v>
+      </c>
+      <c r="C30" s="4">
+        <v>100</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1746,9 +1884,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45678</v>
+      </c>
+      <c r="C31" s="4">
+        <v>100</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1772,9 +1916,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45678</v>
+      </c>
+      <c r="C32" s="4">
+        <v>100</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/74 sanatombi.xlsx
+++ b/LoanOfficer-A/2023/74 sanatombi.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>5100</v>
+        <v>6000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>6900</v>
+        <v>6000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1672,9 +1672,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>45697</v>
+      </c>
+      <c r="G24" s="4">
+        <v>100</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>
@@ -1704,9 +1710,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>45697</v>
+      </c>
+      <c r="G25" s="4">
+        <v>100</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>
@@ -1736,9 +1748,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>45697</v>
+      </c>
+      <c r="G26" s="4">
+        <v>100</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>
@@ -1768,9 +1786,15 @@
       <c r="E27" s="1">
         <v>55</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="3">
+        <v>45697</v>
+      </c>
+      <c r="G27" s="4">
+        <v>100</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
       <c r="I27" s="1">
         <v>85</v>
       </c>
@@ -1800,9 +1824,15 @@
       <c r="E28" s="1">
         <v>56</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="3">
+        <v>45697</v>
+      </c>
+      <c r="G28" s="4">
+        <v>100</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
       <c r="I28" s="1">
         <v>86</v>
       </c>
@@ -1832,9 +1862,15 @@
       <c r="E29" s="1">
         <v>57</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="3">
+        <v>45697</v>
+      </c>
+      <c r="G29" s="4">
+        <v>100</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
       <c r="I29" s="1">
         <v>87</v>
       </c>
@@ -1864,9 +1900,15 @@
       <c r="E30" s="1">
         <v>58</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="3">
+        <v>45697</v>
+      </c>
+      <c r="G30" s="4">
+        <v>100</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
       <c r="I30" s="1">
         <v>88</v>
       </c>
@@ -1896,9 +1938,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>45697</v>
+      </c>
+      <c r="G31" s="4">
+        <v>100</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>
@@ -1928,9 +1976,15 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>45697</v>
+      </c>
+      <c r="G32" s="4">
+        <v>100</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>

--- a/LoanOfficer-A/2023/74 sanatombi.xlsx
+++ b/LoanOfficer-A/2023/74 sanatombi.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -886,9 +886,15 @@
       <c r="I3" s="1">
         <v>61</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K3" s="4">
+        <v>100</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
       <c r="M3" s="1">
         <v>91</v>
       </c>
@@ -924,9 +930,15 @@
       <c r="I4" s="1">
         <v>62</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
+      <c r="J4" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K4" s="4">
+        <v>100</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1">
         <v>92</v>
       </c>
@@ -962,9 +974,15 @@
       <c r="I5" s="1">
         <v>63</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K5" s="4">
+        <v>100</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
       <c r="M5" s="1">
         <v>93</v>
       </c>
@@ -1000,9 +1018,15 @@
       <c r="I6" s="1">
         <v>64</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
+      <c r="J6" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K6" s="4">
+        <v>100</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
       <c r="M6" s="1">
         <v>94</v>
       </c>
@@ -1038,9 +1062,15 @@
       <c r="I7" s="1">
         <v>65</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1"/>
+      <c r="J7" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K7" s="4">
+        <v>100</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
       <c r="M7" s="1">
         <v>95</v>
       </c>
@@ -1076,9 +1106,15 @@
       <c r="I8" s="1">
         <v>66</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="1"/>
+      <c r="J8" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K8" s="4">
+        <v>100</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
       <c r="M8" s="1">
         <v>96</v>
       </c>
@@ -1114,9 +1150,15 @@
       <c r="I9" s="1">
         <v>67</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="1"/>
+      <c r="J9" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K9" s="4">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
       <c r="M9" s="1">
         <v>97</v>
       </c>
@@ -1152,9 +1194,15 @@
       <c r="I10" s="1">
         <v>68</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="1"/>
+      <c r="J10" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K10" s="4">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
       <c r="M10" s="1">
         <v>98</v>
       </c>
@@ -1190,9 +1238,15 @@
       <c r="I11" s="1">
         <v>69</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="1"/>
+      <c r="J11" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K11" s="4">
+        <v>100</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
       <c r="M11" s="1">
         <v>99</v>
       </c>
@@ -1228,9 +1282,15 @@
       <c r="I12" s="1">
         <v>70</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="1"/>
+      <c r="J12" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K12" s="4">
+        <v>100</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
       <c r="M12" s="1">
         <v>100</v>
       </c>
@@ -1266,9 +1326,15 @@
       <c r="I13" s="1">
         <v>71</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="1"/>
+      <c r="J13" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K13" s="4">
+        <v>100</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
       <c r="M13" s="1">
         <v>101</v>
       </c>
@@ -1304,9 +1370,15 @@
       <c r="I14" s="1">
         <v>72</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="1"/>
+      <c r="J14" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K14" s="4">
+        <v>100</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
       <c r="M14" s="1">
         <v>102</v>
       </c>
@@ -1342,9 +1414,15 @@
       <c r="I15" s="1">
         <v>73</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="1"/>
+      <c r="J15" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K15" s="4">
+        <v>100</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
       <c r="M15" s="1">
         <v>103</v>
       </c>
@@ -1380,9 +1458,15 @@
       <c r="I16" s="1">
         <v>74</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="1"/>
+      <c r="J16" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K16" s="4">
+        <v>100</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
       <c r="M16" s="1">
         <v>104</v>
       </c>
@@ -1418,9 +1502,15 @@
       <c r="I17" s="1">
         <v>75</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="1"/>
+      <c r="J17" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K17" s="4">
+        <v>100</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
       <c r="M17" s="1">
         <v>105</v>
       </c>
@@ -1456,9 +1546,15 @@
       <c r="I18" s="1">
         <v>76</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="1"/>
+      <c r="J18" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K18" s="4">
+        <v>100</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
       <c r="M18" s="1">
         <v>106</v>
       </c>
@@ -1494,9 +1590,15 @@
       <c r="I19" s="1">
         <v>77</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K19" s="4">
+        <v>100</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
       <c r="M19" s="1">
         <v>107</v>
       </c>
@@ -1532,9 +1634,15 @@
       <c r="I20" s="1">
         <v>78</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="1"/>
+      <c r="J20" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K20" s="4">
+        <v>100</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
       <c r="M20" s="1">
         <v>108</v>
       </c>
@@ -1570,9 +1678,15 @@
       <c r="I21" s="1">
         <v>79</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="1"/>
+      <c r="J21" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K21" s="4">
+        <v>100</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
       <c r="M21" s="1">
         <v>109</v>
       </c>
@@ -1608,9 +1722,15 @@
       <c r="I22" s="1">
         <v>80</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="1"/>
+      <c r="J22" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K22" s="4">
+        <v>100</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
       <c r="M22" s="1">
         <v>110</v>
       </c>
@@ -1646,9 +1766,15 @@
       <c r="I23" s="1">
         <v>81</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="1"/>
+      <c r="J23" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K23" s="4">
+        <v>100</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
       <c r="M23" s="1">
         <v>111</v>
       </c>
@@ -1684,9 +1810,15 @@
       <c r="I24" s="1">
         <v>82</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="1"/>
+      <c r="J24" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K24" s="4">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
       <c r="M24" s="1">
         <v>112</v>
       </c>
@@ -1722,9 +1854,15 @@
       <c r="I25" s="1">
         <v>83</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="1"/>
+      <c r="J25" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K25" s="4">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
       <c r="M25" s="1">
         <v>113</v>
       </c>
@@ -1760,9 +1898,15 @@
       <c r="I26" s="1">
         <v>84</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="1"/>
+      <c r="J26" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K26" s="4">
+        <v>100</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
       <c r="M26" s="1">
         <v>114</v>
       </c>
@@ -1798,9 +1942,15 @@
       <c r="I27" s="1">
         <v>85</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="1"/>
+      <c r="J27" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K27" s="4">
+        <v>100</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
       <c r="M27" s="1">
         <v>115</v>
       </c>
@@ -1836,9 +1986,15 @@
       <c r="I28" s="1">
         <v>86</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="1"/>
+      <c r="J28" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K28" s="4">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
       <c r="M28" s="1">
         <v>116</v>
       </c>
@@ -1874,9 +2030,15 @@
       <c r="I29" s="1">
         <v>87</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="1"/>
+      <c r="J29" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K29" s="4">
+        <v>100</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
       <c r="M29" s="1">
         <v>117</v>
       </c>
@@ -1912,9 +2074,15 @@
       <c r="I30" s="1">
         <v>88</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="1"/>
+      <c r="J30" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K30" s="4">
+        <v>100</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
       <c r="M30" s="1">
         <v>118</v>
       </c>
@@ -1950,9 +2118,15 @@
       <c r="I31" s="1">
         <v>89</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="1"/>
+      <c r="J31" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K31" s="4">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
       <c r="M31" s="1">
         <v>119</v>
       </c>
@@ -1988,9 +2162,15 @@
       <c r="I32" s="1">
         <v>90</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="1"/>
+      <c r="J32" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K32" s="4">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
       <c r="M32" s="1">
         <v>120</v>
       </c>

--- a/LoanOfficer-A/2023/74 sanatombi.xlsx
+++ b/LoanOfficer-A/2023/74 sanatombi.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -898,9 +898,15 @@
       <c r="M3" s="1">
         <v>91</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="1"/>
+      <c r="N3" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O3" s="4">
+        <v>100</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -942,9 +948,15 @@
       <c r="M4" s="1">
         <v>92</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="1"/>
+      <c r="N4" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O4" s="4">
+        <v>100</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -986,9 +998,15 @@
       <c r="M5" s="1">
         <v>93</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="1"/>
+      <c r="N5" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O5" s="4">
+        <v>100</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1030,9 +1048,15 @@
       <c r="M6" s="1">
         <v>94</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="1"/>
+      <c r="N6" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O6" s="4">
+        <v>100</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1074,9 +1098,15 @@
       <c r="M7" s="1">
         <v>95</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="1"/>
+      <c r="N7" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O7" s="4">
+        <v>100</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1118,9 +1148,15 @@
       <c r="M8" s="1">
         <v>96</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="1"/>
+      <c r="N8" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O8" s="4">
+        <v>100</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1162,9 +1198,15 @@
       <c r="M9" s="1">
         <v>97</v>
       </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="1"/>
+      <c r="N9" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O9" s="4">
+        <v>100</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1206,9 +1248,15 @@
       <c r="M10" s="1">
         <v>98</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="1"/>
+      <c r="N10" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O10" s="4">
+        <v>100</v>
+      </c>
+      <c r="P10" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1250,9 +1298,15 @@
       <c r="M11" s="1">
         <v>99</v>
       </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="1"/>
+      <c r="N11" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O11" s="4">
+        <v>100</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1294,9 +1348,15 @@
       <c r="M12" s="1">
         <v>100</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="1"/>
+      <c r="N12" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O12" s="4">
+        <v>100</v>
+      </c>
+      <c r="P12" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1338,9 +1398,15 @@
       <c r="M13" s="1">
         <v>101</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="1"/>
+      <c r="N13" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O13" s="4">
+        <v>100</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1382,9 +1448,15 @@
       <c r="M14" s="1">
         <v>102</v>
       </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="1"/>
+      <c r="N14" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O14" s="4">
+        <v>100</v>
+      </c>
+      <c r="P14" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1426,9 +1498,15 @@
       <c r="M15" s="1">
         <v>103</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="1"/>
+      <c r="N15" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O15" s="4">
+        <v>100</v>
+      </c>
+      <c r="P15" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -1470,9 +1548,15 @@
       <c r="M16" s="1">
         <v>104</v>
       </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="1"/>
+      <c r="N16" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O16" s="4">
+        <v>100</v>
+      </c>
+      <c r="P16" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1514,9 +1598,15 @@
       <c r="M17" s="1">
         <v>105</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="1"/>
+      <c r="N17" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100</v>
+      </c>
+      <c r="P17" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -1558,9 +1648,15 @@
       <c r="M18" s="1">
         <v>106</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="1"/>
+      <c r="N18" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O18" s="4">
+        <v>100</v>
+      </c>
+      <c r="P18" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -1602,9 +1698,15 @@
       <c r="M19" s="1">
         <v>107</v>
       </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="1"/>
+      <c r="N19" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O19" s="4">
+        <v>100</v>
+      </c>
+      <c r="P19" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -1646,9 +1748,15 @@
       <c r="M20" s="1">
         <v>108</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="1"/>
+      <c r="N20" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O20" s="4">
+        <v>100</v>
+      </c>
+      <c r="P20" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -1690,9 +1798,15 @@
       <c r="M21" s="1">
         <v>109</v>
       </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="1"/>
+      <c r="N21" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O21" s="4">
+        <v>100</v>
+      </c>
+      <c r="P21" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -1734,9 +1848,15 @@
       <c r="M22" s="1">
         <v>110</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="1"/>
+      <c r="N22" s="3">
+        <v>45765</v>
+      </c>
+      <c r="O22" s="4">
+        <v>100</v>
+      </c>
+      <c r="P22" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">

--- a/LoanOfficer-A/2023/74 sanatombi.xlsx
+++ b/LoanOfficer-A/2023/74 sanatombi.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3000" windowWidth="20640" windowHeight="11760" activeTab="1"/>
   </bookViews>
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD20000.18-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="145621" iterateDelta="1E-4"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1898,9 +1898,15 @@
       <c r="M23" s="1">
         <v>111</v>
       </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="1"/>
+      <c r="N23" s="3">
+        <v>45847</v>
+      </c>
+      <c r="O23" s="4">
+        <v>100</v>
+      </c>
+      <c r="P23" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1942,9 +1948,15 @@
       <c r="M24" s="1">
         <v>112</v>
       </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="1"/>
+      <c r="N24" s="3">
+        <v>45847</v>
+      </c>
+      <c r="O24" s="4">
+        <v>100</v>
+      </c>
+      <c r="P24" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -1986,9 +1998,15 @@
       <c r="M25" s="1">
         <v>113</v>
       </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="1"/>
+      <c r="N25" s="3">
+        <v>45847</v>
+      </c>
+      <c r="O25" s="4">
+        <v>100</v>
+      </c>
+      <c r="P25" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -2030,9 +2048,15 @@
       <c r="M26" s="1">
         <v>114</v>
       </c>
-      <c r="N26" s="3"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="1"/>
+      <c r="N26" s="3">
+        <v>45847</v>
+      </c>
+      <c r="O26" s="4">
+        <v>100</v>
+      </c>
+      <c r="P26" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
@@ -2074,9 +2098,15 @@
       <c r="M27" s="1">
         <v>115</v>
       </c>
-      <c r="N27" s="3"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="1"/>
+      <c r="N27" s="3">
+        <v>45847</v>
+      </c>
+      <c r="O27" s="4">
+        <v>100</v>
+      </c>
+      <c r="P27" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
@@ -2118,9 +2148,15 @@
       <c r="M28" s="1">
         <v>116</v>
       </c>
-      <c r="N28" s="3"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="1"/>
+      <c r="N28" s="3">
+        <v>45847</v>
+      </c>
+      <c r="O28" s="4">
+        <v>100</v>
+      </c>
+      <c r="P28" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
@@ -2162,9 +2198,15 @@
       <c r="M29" s="1">
         <v>117</v>
       </c>
-      <c r="N29" s="3"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="1"/>
+      <c r="N29" s="3">
+        <v>45847</v>
+      </c>
+      <c r="O29" s="4">
+        <v>100</v>
+      </c>
+      <c r="P29" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
@@ -2206,9 +2248,15 @@
       <c r="M30" s="1">
         <v>118</v>
       </c>
-      <c r="N30" s="3"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="1"/>
+      <c r="N30" s="3">
+        <v>45847</v>
+      </c>
+      <c r="O30" s="4">
+        <v>100</v>
+      </c>
+      <c r="P30" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
@@ -2250,9 +2298,15 @@
       <c r="M31" s="1">
         <v>119</v>
       </c>
-      <c r="N31" s="3"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="1"/>
+      <c r="N31" s="3">
+        <v>45847</v>
+      </c>
+      <c r="O31" s="4">
+        <v>100</v>
+      </c>
+      <c r="P31" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
@@ -2294,9 +2348,15 @@
       <c r="M32" s="1">
         <v>120</v>
       </c>
-      <c r="N32" s="3"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="1"/>
+      <c r="N32" s="3">
+        <v>45847</v>
+      </c>
+      <c r="O32" s="4">
+        <v>100</v>
+      </c>
+      <c r="P32" s="1">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
